--- a/artfynd/A 2764-2023 artfynd.xlsx
+++ b/artfynd/A 2764-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2764-2023 artfynd.xlsx
+++ b/artfynd/A 2764-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>4700260</v>
       </c>
       <c r="B2" t="n">
-        <v>96925</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457132.5935394361</v>
+        <v>457133</v>
       </c>
       <c r="R2" t="n">
-        <v>6483195.520938593</v>
+        <v>6483196</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1992-07-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1992-07-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>3326494</v>
       </c>
       <c r="B3" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457132.5935394361</v>
+        <v>457133</v>
       </c>
       <c r="R3" t="n">
-        <v>6483195.520938593</v>
+        <v>6483196</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -864,19 +844,9 @@
           <t>1992-07-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1992-07-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 2764-2023 artfynd.xlsx
+++ b/artfynd/A 2764-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4700260</v>
       </c>
       <c r="B2" t="n">
-        <v>99198</v>
+        <v>99206</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3326494</v>
       </c>
       <c r="B3" t="n">
-        <v>106169</v>
+        <v>106181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2764-2023 artfynd.xlsx
+++ b/artfynd/A 2764-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4700260</v>
       </c>
       <c r="B2" t="n">
-        <v>99206</v>
+        <v>99212</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3326494</v>
       </c>
       <c r="B3" t="n">
-        <v>106181</v>
+        <v>106190</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2764-2023 artfynd.xlsx
+++ b/artfynd/A 2764-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4700260</v>
       </c>
       <c r="B2" t="n">
-        <v>99212</v>
+        <v>99215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3326494</v>
       </c>
       <c r="B3" t="n">
-        <v>106190</v>
+        <v>106202</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2764-2023 artfynd.xlsx
+++ b/artfynd/A 2764-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4700260</v>
       </c>
       <c r="B2" t="n">
-        <v>99215</v>
+        <v>99220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3326494</v>
       </c>
       <c r="B3" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2764-2023 artfynd.xlsx
+++ b/artfynd/A 2764-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4700260</v>
       </c>
       <c r="B2" t="n">
-        <v>99220</v>
+        <v>99221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3326494</v>
       </c>
       <c r="B3" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2764-2023 artfynd.xlsx
+++ b/artfynd/A 2764-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4700260</v>
       </c>
       <c r="B2" t="n">
-        <v>99221</v>
+        <v>99248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3326494</v>
       </c>
       <c r="B3" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2764-2023 artfynd.xlsx
+++ b/artfynd/A 2764-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4700260</v>
       </c>
       <c r="B2" t="n">
-        <v>99248</v>
+        <v>99254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3326494</v>
       </c>
       <c r="B3" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2764-2023 artfynd.xlsx
+++ b/artfynd/A 2764-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4700260</v>
       </c>
       <c r="B2" t="n">
-        <v>99254</v>
+        <v>99261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3326494</v>
       </c>
       <c r="B3" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2764-2023 artfynd.xlsx
+++ b/artfynd/A 2764-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4700260</v>
       </c>
       <c r="B2" t="n">
-        <v>99261</v>
+        <v>99265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3326494</v>
       </c>
       <c r="B3" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2764-2023 artfynd.xlsx
+++ b/artfynd/A 2764-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4700260</v>
       </c>
       <c r="B2" t="n">
-        <v>99265</v>
+        <v>99272</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>3326494</v>
       </c>
       <c r="B3" t="n">
-        <v>106261</v>
+        <v>106268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2764-2023 artfynd.xlsx
+++ b/artfynd/A 2764-2023 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4700260</v>
+        <v>3326494</v>
       </c>
       <c r="B2" t="n">
-        <v>99275</v>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222295</v>
+        <v>220785</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårstarr</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carex caryophyllea</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Latourr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -776,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3326494</v>
+        <v>4700260</v>
       </c>
       <c r="B3" t="n">
-        <v>106271</v>
+        <v>99754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220785</v>
+        <v>222295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vårstarr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Carex caryophyllea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Latourr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
